--- a/PccuClub/Template/幹部名冊_template.xlsx
+++ b/PccuClub/Template/幹部名冊_template.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PushuData\2023\Project\Pccu\SRC3\PccuClub\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pccu\SourceCode\SRC2\PccuClub\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F06D14-A548-4CD8-A87C-0B265DC13259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9135"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -41,14 +47,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>任職開始期間</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>任職結束期間</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>學號</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -61,14 +59,22 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>其他</t>
+    <t>任職開始期間 (2026-01-01)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任職結束期間 (2026-01-01)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -421,7 +427,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -430,7 +436,8 @@
     <col min="5" max="5" width="20" customWidth="1" collapsed="1"/>
     <col min="6" max="6" width="20" style="2" customWidth="1" collapsed="1"/>
     <col min="7" max="9" width="20" customWidth="1" collapsed="1"/>
-    <col min="10" max="11" width="20" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="33.42578125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="34.28515625" style="2" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="12" max="12" width="20" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
@@ -445,16 +452,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -463,10 +470,10 @@
         <v>2</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
